--- a/examples/ols_table.xlsx
+++ b/examples/ols_table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eclow\Documents\GitHub\gauss_table_creator\examples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{89F75373-6B5E-4696-B90A-87E0262715BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7581A1FC-1299-447A-817A-9952A1D54A32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{5A3A25E6-4A01-47B0-B297-B6E394D1F611}"/>
   </bookViews>
